--- a/artfynd/A 24725-2021 artfynd.xlsx
+++ b/artfynd/A 24725-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24725-2021 artfynd.xlsx
+++ b/artfynd/A 24725-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY129"/>
+  <dimension ref="A1:AY126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13652,7 +13652,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>96068038</v>
+        <v>96227082</v>
       </c>
       <c r="B107" t="n">
         <v>90647</v>
@@ -13686,19 +13686,26 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Målsjömossen, Vstm</t>
+          <t>Målsjöberget, Vstm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>557476.910599371</v>
+        <v>557452.3242684702</v>
       </c>
       <c r="R107" t="n">
-        <v>6629170.794237452</v>
+        <v>6629228.300204511</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13722,7 +13729,7 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr">
@@ -13732,7 +13739,7 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
@@ -13742,7 +13749,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>BFiV svamputflykt med 21 deltagare. Ledare Lars Bsenko, Tom Sävström och Tina Nordberg.</t>
+          <t>Endast en av minst 3 olika förekomster inom området</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13751,38 +13758,29 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>Barrskog med lövinslag, delvis hällmarker</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>I mossa</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Lars Bsenko</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Lars Bsenko, Bengt Stridh, Tom Sävström, Tina Nordberg, Kenneth Nordberg, Li Dimberg, Urban Dimberg</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>96068056</v>
+        <v>96227087</v>
       </c>
       <c r="B108" t="n">
-        <v>90676</v>
+        <v>90645</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13795,37 +13793,48 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Målsjömossen, Vstm</t>
+          <t>Målsjöberget, Vstm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>557482.0046509879</v>
+        <v>557457.1475205952</v>
       </c>
       <c r="R108" t="n">
-        <v>6629200.067620622</v>
+        <v>6629242.468487837</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13849,7 +13858,7 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
@@ -13859,7 +13868,7 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
@@ -13869,7 +13878,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>BFiV svamputflykt med 21 deltagare. Ledare Lars Bsenko, Tom Sävström och Tina Nordberg.</t>
+          <t>En förekomst i den SÖ delen</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13878,38 +13887,29 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AI108" t="inlineStr">
-        <is>
-          <t>Barrskog med lövinslag, delvis hällmarker</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>I mossa</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Lars Bsenko</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Lars Bsenko, Bengt Stridh, Tom Sävström, Tina Nordberg, Kenneth Nordberg, Li Dimberg, Urban Dimberg</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>96068058</v>
+        <v>96227119</v>
       </c>
       <c r="B109" t="n">
-        <v>90676</v>
+        <v>90669</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13922,37 +13922,44 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Målsjömossen, Vstm</t>
+          <t>Målsjöberget, Vstm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>557280.9172679835</v>
+        <v>557535.684296994</v>
       </c>
       <c r="R109" t="n">
-        <v>6629128.509072396</v>
+        <v>6629380.590750423</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13976,7 +13983,7 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
@@ -13986,7 +13993,7 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
@@ -13996,7 +14003,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>BFiV svamputflykt med 21 deltagare. Ledare Lars Bsenko, Tom Sävström och Tina Nordberg.</t>
+          <t>Två tämligen närstående förekomster</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14005,38 +14012,29 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>Barrskog med lövinslag, delvis hällmarker</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>I mossa</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Lars Bsenko</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Lars Bsenko, Bengt Stridh, Tom Sävström, Tina Nordberg, Kenneth Nordberg, Li Dimberg, Urban Dimberg</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>96227082</v>
+        <v>94745553</v>
       </c>
       <c r="B110" t="n">
-        <v>90647</v>
+        <v>57577</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -14045,45 +14043,55 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4362</v>
+        <v>208249</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Målsjöberget, Vstm</t>
+          <t>Målsjöberget,  Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>557452.3242684702</v>
+        <v>557205.9120209755</v>
       </c>
       <c r="R110" t="n">
-        <v>6629228.300204511</v>
+        <v>6629284.400855203</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -14110,27 +14118,22 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Endast en av minst 3 olika förekomster inom området</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14146,22 +14149,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>96227087</v>
+        <v>103953334</v>
       </c>
       <c r="B111" t="n">
-        <v>90645</v>
+        <v>90653</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -14170,30 +14173,30 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -14205,17 +14208,17 @@
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Målsjöberget, Vstm</t>
+          <t>Målsjömossen, Vstm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>557457.1475205952</v>
+        <v>557372.3836917066</v>
       </c>
       <c r="R111" t="n">
-        <v>6629242.468487837</v>
+        <v>6629213.475955135</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -14239,7 +14242,7 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="Z111" t="inlineStr">
@@ -14249,17 +14252,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>En förekomst i den SÖ delen</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -14272,25 +14270,30 @@
       <c r="AG111" t="b">
         <v>0</v>
       </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>Barrblandskog, inslag av hällmarker</t>
+        </is>
+      </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>96227119</v>
+        <v>103953302</v>
       </c>
       <c r="B112" t="n">
-        <v>90669</v>
+        <v>90653</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -14299,28 +14302,32 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -14330,17 +14337,17 @@
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Målsjöberget, Vstm</t>
+          <t>Målsjömossen, Vstm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>557535.684296994</v>
+        <v>557485.4866404992</v>
       </c>
       <c r="R112" t="n">
-        <v>6629380.590750423</v>
+        <v>6629203.141552035</v>
       </c>
       <c r="S112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -14364,7 +14371,7 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="Z112" t="inlineStr">
@@ -14374,17 +14381,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Två tämligen närstående förekomster</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14397,25 +14399,30 @@
       <c r="AG112" t="b">
         <v>0</v>
       </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>Barrblandskog, inslag av hällmarker</t>
+        </is>
+      </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>94745553</v>
+        <v>103953432</v>
       </c>
       <c r="B113" t="n">
-        <v>57577</v>
+        <v>90649</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14428,21 +14435,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>208249</v>
+        <v>4363</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -14450,32 +14457,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Målsjöberget,  Ramnäs, Vstm, Vstm</t>
+          <t>Målsjömossen, Vstm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>557205.9120209755</v>
+        <v>557366.5845321642</v>
       </c>
       <c r="R113" t="n">
-        <v>6629284.400855203</v>
+        <v>6629033.685492435</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -14499,22 +14500,22 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14527,25 +14528,30 @@
       <c r="AG113" t="b">
         <v>0</v>
       </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>Barrblandskog, inslag av hällmarker</t>
+        </is>
+      </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>103953334</v>
+        <v>103953384</v>
       </c>
       <c r="B114" t="n">
-        <v>90653</v>
+        <v>90676</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14554,30 +14560,30 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -14593,13 +14599,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>557372.3836917066</v>
+        <v>557284.9729345075</v>
       </c>
       <c r="R114" t="n">
-        <v>6629213.475955135</v>
+        <v>6629094.342671412</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14671,7 +14677,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>103953302</v>
+        <v>103953338</v>
       </c>
       <c r="B115" t="n">
         <v>90653</v>
@@ -14706,7 +14712,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -14722,10 +14728,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>557485.4866404992</v>
+        <v>557338.0976721639</v>
       </c>
       <c r="R115" t="n">
-        <v>6629203.141552035</v>
+        <v>6629246.168416119</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14800,10 +14806,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>103953432</v>
+        <v>103953430</v>
       </c>
       <c r="B116" t="n">
-        <v>90649</v>
+        <v>90653</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14816,26 +14822,26 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4363</v>
+        <v>4364</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -14929,10 +14935,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>103953384</v>
+        <v>103953360</v>
       </c>
       <c r="B117" t="n">
-        <v>90676</v>
+        <v>90653</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14941,30 +14947,30 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -14980,13 +14986,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>557284.9729345075</v>
+        <v>557319.1363158979</v>
       </c>
       <c r="R117" t="n">
-        <v>6629094.342671412</v>
+        <v>6629266.010046048</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -15058,7 +15064,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>103953338</v>
+        <v>103953420</v>
       </c>
       <c r="B118" t="n">
         <v>90653</v>
@@ -15109,10 +15115,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>557338.0976721639</v>
+        <v>557278.6360380964</v>
       </c>
       <c r="R118" t="n">
-        <v>6629246.168416119</v>
+        <v>6629047.4316041</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15187,7 +15193,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>103953430</v>
+        <v>103953289</v>
       </c>
       <c r="B119" t="n">
         <v>90653</v>
@@ -15222,7 +15228,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -15238,10 +15244,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>557366.5845321642</v>
+        <v>557503.0660982967</v>
       </c>
       <c r="R119" t="n">
-        <v>6629033.685492435</v>
+        <v>6629240.157920613</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15316,10 +15322,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>103953360</v>
+        <v>103953411</v>
       </c>
       <c r="B120" t="n">
-        <v>90653</v>
+        <v>88806</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -15332,33 +15338,25 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4364</v>
+        <v>5685</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
@@ -15367,10 +15365,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>557319.1363158979</v>
+        <v>557288.8053645898</v>
       </c>
       <c r="R120" t="n">
-        <v>6629266.010046048</v>
+        <v>6629205.644308529</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15428,6 +15426,11 @@
       <c r="AI120" t="inlineStr">
         <is>
           <t>Barrblandskog, inslag av hällmarker</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Murken tallåga, på undersidan.</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15445,7 +15448,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>103953420</v>
+        <v>103953274</v>
       </c>
       <c r="B121" t="n">
         <v>90653</v>
@@ -15480,7 +15483,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -15496,10 +15499,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>557278.6360380964</v>
+        <v>557478.7092693987</v>
       </c>
       <c r="R121" t="n">
-        <v>6629047.4316041</v>
+        <v>6629184.916036985</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15574,10 +15577,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>103953289</v>
+        <v>103953227</v>
       </c>
       <c r="B122" t="n">
-        <v>90653</v>
+        <v>103265</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15590,34 +15593,39 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -15625,10 +15633,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>557503.0660982967</v>
+        <v>557480.7360832581</v>
       </c>
       <c r="R122" t="n">
-        <v>6629240.157920613</v>
+        <v>6629119.007069784</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15673,6 +15681,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Återfynd.</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -15685,7 +15698,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Barrblandskog, inslag av hällmarker</t>
+          <t>Luckig barrblandskog</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -15703,10 +15716,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>103953411</v>
+        <v>103953405</v>
       </c>
       <c r="B123" t="n">
-        <v>88806</v>
+        <v>90653</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15719,25 +15732,33 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5685</v>
+        <v>4364</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
@@ -15807,11 +15828,6 @@
       <c r="AI123" t="inlineStr">
         <is>
           <t>Barrblandskog, inslag av hällmarker</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>Murken tallåga, på undersidan.</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -15829,10 +15845,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>103953274</v>
+        <v>112635669</v>
       </c>
       <c r="B124" t="n">
-        <v>90653</v>
+        <v>104055</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -15845,34 +15861,39 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -15880,10 +15901,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>557478.7092693987</v>
+        <v>557404</v>
       </c>
       <c r="R124" t="n">
-        <v>6629184.916036985</v>
+        <v>6629445</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15910,22 +15931,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15940,7 +15951,12 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>Barrblandskog, inslag av hällmarker</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>i barrförna, mossa under gran</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -15958,10 +15974,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>103953227</v>
+        <v>112635649</v>
       </c>
       <c r="B125" t="n">
-        <v>103265</v>
+        <v>91032</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -15974,39 +15990,26 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
@@ -16014,13 +16017,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>557480.7360832581</v>
+        <v>557337</v>
       </c>
       <c r="R125" t="n">
-        <v>6629119.007069784</v>
+        <v>6629247</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -16044,27 +16047,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Återfynd.</t>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -16079,7 +16067,7 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>Luckig barrblandskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -16097,10 +16085,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>103953405</v>
+        <v>112635657</v>
       </c>
       <c r="B126" t="n">
-        <v>90653</v>
+        <v>91055</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -16109,30 +16097,30 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -16148,13 +16136,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>557288.8053645898</v>
+        <v>557337</v>
       </c>
       <c r="R126" t="n">
-        <v>6629205.644308529</v>
+        <v>6629247</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -16178,22 +16166,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -16208,7 +16186,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>Barrblandskog, inslag av hällmarker</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -16223,365 +16201,6 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>112635669</v>
-      </c>
-      <c r="B127" t="n">
-        <v>104055</v>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E127" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Pyrola chlorantha</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-      <c r="P127" t="inlineStr">
-        <is>
-          <t>Målsjömossen, Vstm</t>
-        </is>
-      </c>
-      <c r="Q127" t="n">
-        <v>557404</v>
-      </c>
-      <c r="R127" t="n">
-        <v>6629445</v>
-      </c>
-      <c r="S127" t="n">
-        <v>10</v>
-      </c>
-      <c r="T127" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V127" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W127" t="inlineStr">
-        <is>
-          <t>Ramnäs</t>
-        </is>
-      </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>2023-10-09</t>
-        </is>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>2023-10-09</t>
-        </is>
-      </c>
-      <c r="AD127" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE127" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF127" t="inlineStr"/>
-      <c r="AG127" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>i barrförna, mossa under gran</t>
-        </is>
-      </c>
-      <c r="AT127" t="inlineStr"/>
-      <c r="AW127" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AX127" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY127" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>112635649</v>
-      </c>
-      <c r="B128" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E128" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="P128" t="inlineStr">
-        <is>
-          <t>Målsjömossen, Vstm</t>
-        </is>
-      </c>
-      <c r="Q128" t="n">
-        <v>557337</v>
-      </c>
-      <c r="R128" t="n">
-        <v>6629247</v>
-      </c>
-      <c r="S128" t="n">
-        <v>25</v>
-      </c>
-      <c r="T128" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U128" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>Ramnäs</t>
-        </is>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>2023-10-09</t>
-        </is>
-      </c>
-      <c r="AA128" t="inlineStr">
-        <is>
-          <t>2023-10-09</t>
-        </is>
-      </c>
-      <c r="AD128" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE128" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF128" t="inlineStr"/>
-      <c r="AG128" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AT128" t="inlineStr"/>
-      <c r="AW128" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AX128" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY128" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>112635657</v>
-      </c>
-      <c r="B129" t="n">
-        <v>91055</v>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E129" t="n">
-        <v>5966</v>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
-      <c r="P129" t="inlineStr">
-        <is>
-          <t>Målsjömossen, Vstm</t>
-        </is>
-      </c>
-      <c r="Q129" t="n">
-        <v>557337</v>
-      </c>
-      <c r="R129" t="n">
-        <v>6629247</v>
-      </c>
-      <c r="S129" t="n">
-        <v>25</v>
-      </c>
-      <c r="T129" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U129" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V129" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W129" t="inlineStr">
-        <is>
-          <t>Ramnäs</t>
-        </is>
-      </c>
-      <c r="Y129" t="inlineStr">
-        <is>
-          <t>2023-10-09</t>
-        </is>
-      </c>
-      <c r="AA129" t="inlineStr">
-        <is>
-          <t>2023-10-09</t>
-        </is>
-      </c>
-      <c r="AD129" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE129" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF129" t="inlineStr"/>
-      <c r="AG129" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AT129" t="inlineStr"/>
-      <c r="AW129" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AX129" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY129" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24725-2021 artfynd.xlsx
+++ b/artfynd/A 24725-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY126"/>
+  <dimension ref="A1:AY145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16202,6 +16202,2169 @@
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>128846310</v>
+      </c>
+      <c r="B127" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Målsjömossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>557309</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6629033</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>128846369</v>
+      </c>
+      <c r="B128" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Målsjömossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>557263</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6629182</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128846508</v>
+      </c>
+      <c r="B129" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Målsjömossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>557354</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6629232</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF129" t="inlineStr"/>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128846350</v>
+      </c>
+      <c r="B130" t="n">
+        <v>90876</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Målsjömossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>557291</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6629099</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF130" t="inlineStr"/>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>128846202</v>
+      </c>
+      <c r="B131" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Målsjömossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>557363</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6629044</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF131" t="inlineStr"/>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>128846303</v>
+      </c>
+      <c r="B132" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Målsjömossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>557337</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6629033</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF132" t="inlineStr"/>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>128846467</v>
+      </c>
+      <c r="B133" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Målsjömossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>557322</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6629269</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF133" t="inlineStr"/>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>128846316</v>
+      </c>
+      <c r="B134" t="n">
+        <v>92820</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Målsjömossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>557309</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6629033</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF134" t="inlineStr"/>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>128846299</v>
+      </c>
+      <c r="B135" t="n">
+        <v>92820</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Målsjömossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>557337</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6629033</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF135" t="inlineStr"/>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>128846693</v>
+      </c>
+      <c r="B136" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Målsjömossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>557426</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6629174</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF136" t="inlineStr"/>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>Barrblandskog, hällmark</t>
+        </is>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>128846347</v>
+      </c>
+      <c r="B137" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Målsjömossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>557291</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6629099</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF137" t="inlineStr"/>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>128846187</v>
+      </c>
+      <c r="B138" t="n">
+        <v>92796</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Målsjömossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>557368</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6629121</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF138" t="inlineStr"/>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>128846704</v>
+      </c>
+      <c r="B139" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Målsjömossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>557432</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6629153</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF139" t="inlineStr"/>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>Barrblandskog, hällmark</t>
+        </is>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>128846640</v>
+      </c>
+      <c r="B140" t="n">
+        <v>92820</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Målsjömossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>557430</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6629202</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF140" t="inlineStr"/>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>Barrblandskog, hällmark</t>
+        </is>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>128846488</v>
+      </c>
+      <c r="B141" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Målsjömossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>557343</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6629242</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF141" t="inlineStr"/>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>128846543</v>
+      </c>
+      <c r="B142" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Målsjömossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>557383</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6629221</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF142" t="inlineStr"/>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>128846394</v>
+      </c>
+      <c r="B143" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Målsjömossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>557229</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6629256</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF143" t="inlineStr"/>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>128846477</v>
+      </c>
+      <c r="B144" t="n">
+        <v>92820</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Målsjömossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>557322</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6629269</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF144" t="inlineStr"/>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>128846335</v>
+      </c>
+      <c r="B145" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Målsjömossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>557277</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6629049</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF145" t="inlineStr"/>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24725-2021 artfynd.xlsx
+++ b/artfynd/A 24725-2021 artfynd.xlsx
@@ -16207,7 +16207,7 @@
         <v>128846310</v>
       </c>
       <c r="B127" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>128846369</v>
       </c>
       <c r="B128" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>128846508</v>
       </c>
       <c r="B129" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>128846350</v>
       </c>
       <c r="B130" t="n">
-        <v>90876</v>
+        <v>90881</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>128846202</v>
       </c>
       <c r="B131" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>128846303</v>
       </c>
       <c r="B132" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>128846467</v>
       </c>
       <c r="B133" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>128846316</v>
       </c>
       <c r="B134" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>128846299</v>
       </c>
       <c r="B135" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>128846693</v>
       </c>
       <c r="B136" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>128846347</v>
       </c>
       <c r="B137" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17455,37 +17455,37 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128846187</v>
+        <v>128846640</v>
       </c>
       <c r="B138" t="n">
-        <v>92796</v>
+        <v>92825</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -17501,10 +17501,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>557368</v>
+        <v>557430</v>
       </c>
       <c r="R138" t="n">
-        <v>6629121</v>
+        <v>6629202</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, hällmark</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -17569,10 +17569,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128846704</v>
+        <v>128846187</v>
       </c>
       <c r="B139" t="n">
-        <v>92784</v>
+        <v>92801</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17580,26 +17580,26 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -17615,10 +17615,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>557432</v>
+        <v>557368</v>
       </c>
       <c r="R139" t="n">
-        <v>6629153</v>
+        <v>6629121</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -17665,7 +17665,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmark</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -17683,37 +17683,37 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128846640</v>
+        <v>128846488</v>
       </c>
       <c r="B140" t="n">
-        <v>92820</v>
+        <v>92789</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -17729,10 +17729,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>557430</v>
+        <v>557343</v>
       </c>
       <c r="R140" t="n">
-        <v>6629202</v>
+        <v>6629242</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -17779,7 +17779,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmark</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -17797,10 +17797,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128846488</v>
+        <v>128846704</v>
       </c>
       <c r="B141" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -17843,10 +17843,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>557343</v>
+        <v>557432</v>
       </c>
       <c r="R141" t="n">
-        <v>6629242</v>
+        <v>6629153</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17893,7 +17893,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, hällmark</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -17914,7 +17914,7 @@
         <v>128846543</v>
       </c>
       <c r="B142" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -18025,10 +18025,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128846394</v>
+        <v>128846335</v>
       </c>
       <c r="B143" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -18071,10 +18071,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>557229</v>
+        <v>557277</v>
       </c>
       <c r="R143" t="n">
-        <v>6629256</v>
+        <v>6629049</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -18139,37 +18139,37 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128846477</v>
+        <v>128846394</v>
       </c>
       <c r="B144" t="n">
-        <v>92820</v>
+        <v>92789</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -18185,10 +18185,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>557322</v>
+        <v>557229</v>
       </c>
       <c r="R144" t="n">
-        <v>6629269</v>
+        <v>6629256</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -18253,37 +18253,37 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128846335</v>
+        <v>128846477</v>
       </c>
       <c r="B145" t="n">
-        <v>92784</v>
+        <v>92825</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -18299,10 +18299,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>557277</v>
+        <v>557322</v>
       </c>
       <c r="R145" t="n">
-        <v>6629049</v>
+        <v>6629269</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>

--- a/artfynd/A 24725-2021 artfynd.xlsx
+++ b/artfynd/A 24725-2021 artfynd.xlsx
@@ -16885,37 +16885,37 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128846316</v>
+        <v>128846467</v>
       </c>
       <c r="B133" t="n">
-        <v>92849</v>
+        <v>92811</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -16931,10 +16931,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>557309</v>
+        <v>557322</v>
       </c>
       <c r="R133" t="n">
-        <v>6629033</v>
+        <v>6629269</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16999,37 +16999,37 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128846467</v>
+        <v>128846316</v>
       </c>
       <c r="B134" t="n">
-        <v>92811</v>
+        <v>92849</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -17045,10 +17045,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>557322</v>
+        <v>557309</v>
       </c>
       <c r="R134" t="n">
-        <v>6629269</v>
+        <v>6629033</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -17455,37 +17455,37 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128846640</v>
+        <v>128846187</v>
       </c>
       <c r="B138" t="n">
-        <v>92849</v>
+        <v>92823</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -17501,10 +17501,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>557430</v>
+        <v>557368</v>
       </c>
       <c r="R138" t="n">
-        <v>6629202</v>
+        <v>6629121</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmark</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -17569,10 +17569,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128846187</v>
+        <v>128846704</v>
       </c>
       <c r="B139" t="n">
-        <v>92823</v>
+        <v>92811</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17580,26 +17580,26 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -17615,10 +17615,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>557368</v>
+        <v>557432</v>
       </c>
       <c r="R139" t="n">
-        <v>6629121</v>
+        <v>6629153</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -17665,7 +17665,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, hällmark</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -17683,7 +17683,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128846704</v>
+        <v>128846488</v>
       </c>
       <c r="B140" t="n">
         <v>92811</v>
@@ -17713,7 +17713,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -17729,10 +17729,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>557432</v>
+        <v>557343</v>
       </c>
       <c r="R140" t="n">
-        <v>6629153</v>
+        <v>6629242</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -17779,7 +17779,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmark</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -17797,37 +17797,37 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128846488</v>
+        <v>128846640</v>
       </c>
       <c r="B141" t="n">
-        <v>92811</v>
+        <v>92849</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -17843,10 +17843,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>557343</v>
+        <v>557430</v>
       </c>
       <c r="R141" t="n">
-        <v>6629242</v>
+        <v>6629202</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17893,7 +17893,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, hällmark</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>

--- a/artfynd/A 24725-2021 artfynd.xlsx
+++ b/artfynd/A 24725-2021 artfynd.xlsx
@@ -16207,7 +16207,7 @@
         <v>128846310</v>
       </c>
       <c r="B127" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>128846369</v>
       </c>
       <c r="B128" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>128846350</v>
       </c>
       <c r="B129" t="n">
-        <v>90902</v>
+        <v>90905</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>128846508</v>
       </c>
       <c r="B130" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>128846202</v>
       </c>
       <c r="B131" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>128846303</v>
       </c>
       <c r="B132" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16885,37 +16885,37 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128846467</v>
+        <v>128846316</v>
       </c>
       <c r="B133" t="n">
-        <v>92811</v>
+        <v>92854</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -16931,10 +16931,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>557322</v>
+        <v>557309</v>
       </c>
       <c r="R133" t="n">
-        <v>6629269</v>
+        <v>6629033</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16999,37 +16999,37 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128846316</v>
+        <v>128846467</v>
       </c>
       <c r="B134" t="n">
-        <v>92849</v>
+        <v>92816</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -17045,10 +17045,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>557309</v>
+        <v>557322</v>
       </c>
       <c r="R134" t="n">
-        <v>6629033</v>
+        <v>6629269</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -17116,7 +17116,7 @@
         <v>128846299</v>
       </c>
       <c r="B135" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>128846693</v>
       </c>
       <c r="B136" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>128846347</v>
       </c>
       <c r="B137" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17455,37 +17455,37 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128846187</v>
+        <v>128846640</v>
       </c>
       <c r="B138" t="n">
-        <v>92823</v>
+        <v>92854</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -17501,10 +17501,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>557368</v>
+        <v>557430</v>
       </c>
       <c r="R138" t="n">
-        <v>6629121</v>
+        <v>6629202</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, hällmark</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -17569,10 +17569,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128846704</v>
+        <v>128846187</v>
       </c>
       <c r="B139" t="n">
-        <v>92811</v>
+        <v>92828</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17580,26 +17580,26 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -17615,10 +17615,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>557432</v>
+        <v>557368</v>
       </c>
       <c r="R139" t="n">
-        <v>6629153</v>
+        <v>6629121</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -17665,7 +17665,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmark</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -17683,10 +17683,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128846488</v>
+        <v>128846704</v>
       </c>
       <c r="B140" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -17729,10 +17729,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>557343</v>
+        <v>557432</v>
       </c>
       <c r="R140" t="n">
-        <v>6629242</v>
+        <v>6629153</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -17779,7 +17779,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, hällmark</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -17797,37 +17797,37 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128846640</v>
+        <v>128846488</v>
       </c>
       <c r="B141" t="n">
-        <v>92849</v>
+        <v>92816</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -17843,10 +17843,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>557430</v>
+        <v>557343</v>
       </c>
       <c r="R141" t="n">
-        <v>6629202</v>
+        <v>6629242</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17893,7 +17893,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmark</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -17914,7 +17914,7 @@
         <v>128846543</v>
       </c>
       <c r="B142" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -18025,37 +18025,37 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128846394</v>
+        <v>128846477</v>
       </c>
       <c r="B143" t="n">
-        <v>92811</v>
+        <v>92854</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -18071,10 +18071,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>557229</v>
+        <v>557322</v>
       </c>
       <c r="R143" t="n">
-        <v>6629256</v>
+        <v>6629269</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -18139,10 +18139,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128846335</v>
+        <v>128846394</v>
       </c>
       <c r="B144" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -18185,10 +18185,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>557277</v>
+        <v>557229</v>
       </c>
       <c r="R144" t="n">
-        <v>6629049</v>
+        <v>6629256</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -18253,37 +18253,37 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128846477</v>
+        <v>128846335</v>
       </c>
       <c r="B145" t="n">
-        <v>92849</v>
+        <v>92816</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -18299,10 +18299,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>557322</v>
+        <v>557277</v>
       </c>
       <c r="R145" t="n">
-        <v>6629269</v>
+        <v>6629049</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>

--- a/artfynd/A 24725-2021 artfynd.xlsx
+++ b/artfynd/A 24725-2021 artfynd.xlsx
@@ -16207,7 +16207,7 @@
         <v>128846310</v>
       </c>
       <c r="B127" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>128846369</v>
       </c>
       <c r="B128" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>128846350</v>
       </c>
       <c r="B129" t="n">
-        <v>90905</v>
+        <v>90908</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>128846508</v>
       </c>
       <c r="B130" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>128846202</v>
       </c>
       <c r="B131" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>128846303</v>
       </c>
       <c r="B132" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16885,37 +16885,37 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128846316</v>
+        <v>128846467</v>
       </c>
       <c r="B133" t="n">
-        <v>92854</v>
+        <v>92819</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -16931,10 +16931,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>557309</v>
+        <v>557322</v>
       </c>
       <c r="R133" t="n">
-        <v>6629033</v>
+        <v>6629269</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16999,37 +16999,37 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128846467</v>
+        <v>128846316</v>
       </c>
       <c r="B134" t="n">
-        <v>92816</v>
+        <v>92857</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -17045,10 +17045,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>557322</v>
+        <v>557309</v>
       </c>
       <c r="R134" t="n">
-        <v>6629269</v>
+        <v>6629033</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -17116,7 +17116,7 @@
         <v>128846299</v>
       </c>
       <c r="B135" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>128846693</v>
       </c>
       <c r="B136" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>128846347</v>
       </c>
       <c r="B137" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17455,37 +17455,37 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128846640</v>
+        <v>128846187</v>
       </c>
       <c r="B138" t="n">
-        <v>92854</v>
+        <v>92831</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -17501,10 +17501,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>557430</v>
+        <v>557368</v>
       </c>
       <c r="R138" t="n">
-        <v>6629202</v>
+        <v>6629121</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmark</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -17569,10 +17569,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128846187</v>
+        <v>128846704</v>
       </c>
       <c r="B139" t="n">
-        <v>92828</v>
+        <v>92819</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17580,26 +17580,26 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -17615,10 +17615,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>557368</v>
+        <v>557432</v>
       </c>
       <c r="R139" t="n">
-        <v>6629121</v>
+        <v>6629153</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -17665,7 +17665,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, hällmark</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -17683,10 +17683,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128846704</v>
+        <v>128846488</v>
       </c>
       <c r="B140" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -17729,10 +17729,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>557432</v>
+        <v>557343</v>
       </c>
       <c r="R140" t="n">
-        <v>6629153</v>
+        <v>6629242</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -17779,7 +17779,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmark</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -17797,37 +17797,37 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128846488</v>
+        <v>128846640</v>
       </c>
       <c r="B141" t="n">
-        <v>92816</v>
+        <v>92857</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -17843,10 +17843,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>557343</v>
+        <v>557430</v>
       </c>
       <c r="R141" t="n">
-        <v>6629242</v>
+        <v>6629202</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17893,7 +17893,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, hällmark</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -17914,7 +17914,7 @@
         <v>128846543</v>
       </c>
       <c r="B142" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>128846477</v>
       </c>
       <c r="B143" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>128846394</v>
       </c>
       <c r="B144" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>128846335</v>
       </c>
       <c r="B145" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 24725-2021 artfynd.xlsx
+++ b/artfynd/A 24725-2021 artfynd.xlsx
@@ -18025,37 +18025,37 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128846477</v>
+        <v>128846394</v>
       </c>
       <c r="B143" t="n">
-        <v>92857</v>
+        <v>92819</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -18071,10 +18071,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>557322</v>
+        <v>557229</v>
       </c>
       <c r="R143" t="n">
-        <v>6629269</v>
+        <v>6629256</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -18139,37 +18139,37 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128846394</v>
+        <v>128846477</v>
       </c>
       <c r="B144" t="n">
-        <v>92819</v>
+        <v>92857</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -18185,10 +18185,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>557229</v>
+        <v>557322</v>
       </c>
       <c r="R144" t="n">
-        <v>6629256</v>
+        <v>6629269</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>

--- a/artfynd/A 24725-2021 artfynd.xlsx
+++ b/artfynd/A 24725-2021 artfynd.xlsx
@@ -16432,10 +16432,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128846350</v>
+        <v>128846508</v>
       </c>
       <c r="B129" t="n">
-        <v>90908</v>
+        <v>92819</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16443,25 +16443,33 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5685</v>
+        <v>4364</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
@@ -16470,10 +16478,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>557291</v>
+        <v>557354</v>
       </c>
       <c r="R129" t="n">
-        <v>6629099</v>
+        <v>6629232</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -16521,11 +16529,6 @@
       <c r="AI129" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO129" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -16543,10 +16546,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128846508</v>
+        <v>128846350</v>
       </c>
       <c r="B130" t="n">
-        <v>92819</v>
+        <v>90908</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16554,33 +16557,25 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4364</v>
+        <v>5685</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
@@ -16589,10 +16584,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>557354</v>
+        <v>557291</v>
       </c>
       <c r="R130" t="n">
-        <v>6629232</v>
+        <v>6629099</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -16640,6 +16635,11 @@
       <c r="AI130" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
@@ -17569,7 +17569,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128846704</v>
+        <v>128846488</v>
       </c>
       <c r="B139" t="n">
         <v>92819</v>
@@ -17599,7 +17599,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -17615,10 +17615,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>557432</v>
+        <v>557343</v>
       </c>
       <c r="R139" t="n">
-        <v>6629153</v>
+        <v>6629242</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -17665,7 +17665,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmark</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -17683,37 +17683,37 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128846488</v>
+        <v>128846640</v>
       </c>
       <c r="B140" t="n">
-        <v>92819</v>
+        <v>92857</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -17729,10 +17729,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>557343</v>
+        <v>557430</v>
       </c>
       <c r="R140" t="n">
-        <v>6629242</v>
+        <v>6629202</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -17779,7 +17779,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, hällmark</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -17797,37 +17797,37 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128846640</v>
+        <v>128846704</v>
       </c>
       <c r="B141" t="n">
-        <v>92857</v>
+        <v>92819</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -17843,10 +17843,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>557430</v>
+        <v>557432</v>
       </c>
       <c r="R141" t="n">
-        <v>6629202</v>
+        <v>6629153</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -18025,7 +18025,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128846394</v>
+        <v>128846335</v>
       </c>
       <c r="B143" t="n">
         <v>92819</v>
@@ -18055,7 +18055,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -18071,10 +18071,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>557229</v>
+        <v>557277</v>
       </c>
       <c r="R143" t="n">
-        <v>6629256</v>
+        <v>6629049</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -18139,37 +18139,37 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128846477</v>
+        <v>128846394</v>
       </c>
       <c r="B144" t="n">
-        <v>92857</v>
+        <v>92819</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -18185,10 +18185,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>557322</v>
+        <v>557229</v>
       </c>
       <c r="R144" t="n">
-        <v>6629269</v>
+        <v>6629256</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -18253,37 +18253,37 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128846335</v>
+        <v>128846477</v>
       </c>
       <c r="B145" t="n">
-        <v>92819</v>
+        <v>92857</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -18299,10 +18299,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>557277</v>
+        <v>557322</v>
       </c>
       <c r="R145" t="n">
-        <v>6629049</v>
+        <v>6629269</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>

--- a/artfynd/A 24725-2021 artfynd.xlsx
+++ b/artfynd/A 24725-2021 artfynd.xlsx
@@ -16207,7 +16207,7 @@
         <v>128846310</v>
       </c>
       <c r="B127" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>128846369</v>
       </c>
       <c r="B128" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>128846508</v>
       </c>
       <c r="B129" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>128846350</v>
       </c>
       <c r="B130" t="n">
-        <v>90908</v>
+        <v>90912</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>128846202</v>
       </c>
       <c r="B131" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>128846303</v>
       </c>
       <c r="B132" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>128846467</v>
       </c>
       <c r="B133" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>128846316</v>
       </c>
       <c r="B134" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>128846299</v>
       </c>
       <c r="B135" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>128846693</v>
       </c>
       <c r="B136" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>128846347</v>
       </c>
       <c r="B137" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>128846187</v>
       </c>
       <c r="B138" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17569,10 +17569,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128846488</v>
+        <v>128846704</v>
       </c>
       <c r="B139" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -17615,10 +17615,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>557343</v>
+        <v>557432</v>
       </c>
       <c r="R139" t="n">
-        <v>6629242</v>
+        <v>6629153</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -17665,7 +17665,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, hällmark</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -17683,37 +17683,37 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128846640</v>
+        <v>128846488</v>
       </c>
       <c r="B140" t="n">
-        <v>92857</v>
+        <v>92826</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -17729,10 +17729,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>557430</v>
+        <v>557343</v>
       </c>
       <c r="R140" t="n">
-        <v>6629202</v>
+        <v>6629242</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -17779,7 +17779,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmark</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -17797,37 +17797,37 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128846704</v>
+        <v>128846640</v>
       </c>
       <c r="B141" t="n">
-        <v>92819</v>
+        <v>92864</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -17843,10 +17843,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>557432</v>
+        <v>557430</v>
       </c>
       <c r="R141" t="n">
-        <v>6629153</v>
+        <v>6629202</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17914,7 +17914,7 @@
         <v>128846543</v>
       </c>
       <c r="B142" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -18025,10 +18025,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128846335</v>
+        <v>128846394</v>
       </c>
       <c r="B143" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -18071,10 +18071,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>557277</v>
+        <v>557229</v>
       </c>
       <c r="R143" t="n">
-        <v>6629049</v>
+        <v>6629256</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -18139,10 +18139,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128846394</v>
+        <v>128846335</v>
       </c>
       <c r="B144" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -18185,10 +18185,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>557229</v>
+        <v>557277</v>
       </c>
       <c r="R144" t="n">
-        <v>6629256</v>
+        <v>6629049</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -18256,7 +18256,7 @@
         <v>128846477</v>
       </c>
       <c r="B145" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 24725-2021 artfynd.xlsx
+++ b/artfynd/A 24725-2021 artfynd.xlsx
@@ -17455,37 +17455,37 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128846187</v>
+        <v>128846640</v>
       </c>
       <c r="B138" t="n">
-        <v>92838</v>
+        <v>92864</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -17501,10 +17501,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>557368</v>
+        <v>557430</v>
       </c>
       <c r="R138" t="n">
-        <v>6629121</v>
+        <v>6629202</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, hällmark</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -17569,10 +17569,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128846704</v>
+        <v>128846187</v>
       </c>
       <c r="B139" t="n">
-        <v>92826</v>
+        <v>92838</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17580,26 +17580,26 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -17615,10 +17615,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>557432</v>
+        <v>557368</v>
       </c>
       <c r="R139" t="n">
-        <v>6629153</v>
+        <v>6629121</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -17665,7 +17665,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmark</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -17683,7 +17683,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128846488</v>
+        <v>128846704</v>
       </c>
       <c r="B140" t="n">
         <v>92826</v>
@@ -17713,7 +17713,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -17729,10 +17729,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>557343</v>
+        <v>557432</v>
       </c>
       <c r="R140" t="n">
-        <v>6629242</v>
+        <v>6629153</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -17779,7 +17779,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, hällmark</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -17797,37 +17797,37 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128846640</v>
+        <v>128846488</v>
       </c>
       <c r="B141" t="n">
-        <v>92864</v>
+        <v>92826</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -17843,10 +17843,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>557430</v>
+        <v>557343</v>
       </c>
       <c r="R141" t="n">
-        <v>6629202</v>
+        <v>6629242</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17893,7 +17893,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmark</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>

--- a/artfynd/A 24725-2021 artfynd.xlsx
+++ b/artfynd/A 24725-2021 artfynd.xlsx
@@ -16207,7 +16207,7 @@
         <v>128846310</v>
       </c>
       <c r="B127" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>128846369</v>
       </c>
       <c r="B128" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>128846508</v>
       </c>
       <c r="B129" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>128846350</v>
       </c>
       <c r="B130" t="n">
-        <v>90912</v>
+        <v>90919</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>128846202</v>
       </c>
       <c r="B131" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>128846303</v>
       </c>
       <c r="B132" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>128846467</v>
       </c>
       <c r="B133" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>128846316</v>
       </c>
       <c r="B134" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>128846299</v>
       </c>
       <c r="B135" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>128846693</v>
       </c>
       <c r="B136" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>128846347</v>
       </c>
       <c r="B137" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17455,37 +17455,37 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128846640</v>
+        <v>128846187</v>
       </c>
       <c r="B138" t="n">
-        <v>92864</v>
+        <v>92845</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -17501,10 +17501,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>557430</v>
+        <v>557368</v>
       </c>
       <c r="R138" t="n">
-        <v>6629202</v>
+        <v>6629121</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmark</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -17569,10 +17569,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128846187</v>
+        <v>128846488</v>
       </c>
       <c r="B139" t="n">
-        <v>92838</v>
+        <v>92833</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17580,26 +17580,26 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -17615,10 +17615,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>557368</v>
+        <v>557343</v>
       </c>
       <c r="R139" t="n">
-        <v>6629121</v>
+        <v>6629242</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -17686,7 +17686,7 @@
         <v>128846704</v>
       </c>
       <c r="B140" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17797,37 +17797,37 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128846488</v>
+        <v>128846640</v>
       </c>
       <c r="B141" t="n">
-        <v>92826</v>
+        <v>92871</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -17843,10 +17843,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>557343</v>
+        <v>557430</v>
       </c>
       <c r="R141" t="n">
-        <v>6629242</v>
+        <v>6629202</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17893,7 +17893,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, hällmark</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -17914,7 +17914,7 @@
         <v>128846543</v>
       </c>
       <c r="B142" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -18025,37 +18025,37 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128846394</v>
+        <v>128846477</v>
       </c>
       <c r="B143" t="n">
-        <v>92826</v>
+        <v>92871</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -18071,10 +18071,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>557229</v>
+        <v>557322</v>
       </c>
       <c r="R143" t="n">
-        <v>6629256</v>
+        <v>6629269</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -18142,7 +18142,7 @@
         <v>128846335</v>
       </c>
       <c r="B144" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18253,37 +18253,37 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128846477</v>
+        <v>128846394</v>
       </c>
       <c r="B145" t="n">
-        <v>92864</v>
+        <v>92833</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -18299,10 +18299,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>557322</v>
+        <v>557229</v>
       </c>
       <c r="R145" t="n">
-        <v>6629269</v>
+        <v>6629256</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>

--- a/artfynd/A 24725-2021 artfynd.xlsx
+++ b/artfynd/A 24725-2021 artfynd.xlsx
@@ -16207,7 +16207,7 @@
         <v>128846310</v>
       </c>
       <c r="B127" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>128846369</v>
       </c>
       <c r="B128" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>128846508</v>
       </c>
       <c r="B129" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>128846350</v>
       </c>
       <c r="B130" t="n">
-        <v>90919</v>
+        <v>90921</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>128846202</v>
       </c>
       <c r="B131" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>128846303</v>
       </c>
       <c r="B132" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>128846467</v>
       </c>
       <c r="B133" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>128846316</v>
       </c>
       <c r="B134" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>128846299</v>
       </c>
       <c r="B135" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>128846693</v>
       </c>
       <c r="B136" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>128846347</v>
       </c>
       <c r="B137" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>128846187</v>
       </c>
       <c r="B138" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17569,10 +17569,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128846488</v>
+        <v>128846704</v>
       </c>
       <c r="B139" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -17615,10 +17615,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>557343</v>
+        <v>557432</v>
       </c>
       <c r="R139" t="n">
-        <v>6629242</v>
+        <v>6629153</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -17665,7 +17665,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, hällmark</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -17683,10 +17683,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128846704</v>
+        <v>128846488</v>
       </c>
       <c r="B140" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -17729,10 +17729,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>557432</v>
+        <v>557343</v>
       </c>
       <c r="R140" t="n">
-        <v>6629153</v>
+        <v>6629242</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -17779,7 +17779,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmark</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -17800,7 +17800,7 @@
         <v>128846640</v>
       </c>
       <c r="B141" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>128846543</v>
       </c>
       <c r="B142" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -18025,37 +18025,37 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128846477</v>
+        <v>128846394</v>
       </c>
       <c r="B143" t="n">
-        <v>92871</v>
+        <v>92835</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -18071,10 +18071,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>557322</v>
+        <v>557229</v>
       </c>
       <c r="R143" t="n">
-        <v>6629269</v>
+        <v>6629256</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -18142,7 +18142,7 @@
         <v>128846335</v>
       </c>
       <c r="B144" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18253,37 +18253,37 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128846394</v>
+        <v>128846477</v>
       </c>
       <c r="B145" t="n">
-        <v>92833</v>
+        <v>92873</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -18299,10 +18299,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>557229</v>
+        <v>557322</v>
       </c>
       <c r="R145" t="n">
-        <v>6629256</v>
+        <v>6629269</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>

--- a/artfynd/A 24725-2021 artfynd.xlsx
+++ b/artfynd/A 24725-2021 artfynd.xlsx
@@ -16432,10 +16432,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128846508</v>
+        <v>128846350</v>
       </c>
       <c r="B129" t="n">
-        <v>92835</v>
+        <v>90921</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16443,33 +16443,25 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4364</v>
+        <v>5685</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
@@ -16478,10 +16470,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>557354</v>
+        <v>557291</v>
       </c>
       <c r="R129" t="n">
-        <v>6629232</v>
+        <v>6629099</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -16529,6 +16521,11 @@
       <c r="AI129" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -16546,10 +16543,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128846350</v>
+        <v>128846508</v>
       </c>
       <c r="B130" t="n">
-        <v>90921</v>
+        <v>92835</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16557,25 +16554,33 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5685</v>
+        <v>4364</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
@@ -16584,10 +16589,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>557291</v>
+        <v>557354</v>
       </c>
       <c r="R130" t="n">
-        <v>6629099</v>
+        <v>6629232</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -16635,11 +16640,6 @@
       <c r="AI130" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
@@ -17455,37 +17455,37 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128846187</v>
+        <v>128846640</v>
       </c>
       <c r="B138" t="n">
-        <v>92847</v>
+        <v>92873</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -17501,10 +17501,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>557368</v>
+        <v>557430</v>
       </c>
       <c r="R138" t="n">
-        <v>6629121</v>
+        <v>6629202</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, hällmark</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -17797,37 +17797,37 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128846640</v>
+        <v>128846187</v>
       </c>
       <c r="B141" t="n">
-        <v>92873</v>
+        <v>92847</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -17843,10 +17843,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>557430</v>
+        <v>557368</v>
       </c>
       <c r="R141" t="n">
-        <v>6629202</v>
+        <v>6629121</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17893,7 +17893,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmark</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>

--- a/artfynd/A 24725-2021 artfynd.xlsx
+++ b/artfynd/A 24725-2021 artfynd.xlsx
@@ -16432,10 +16432,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128846350</v>
+        <v>128846508</v>
       </c>
       <c r="B129" t="n">
-        <v>90921</v>
+        <v>92835</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16443,25 +16443,33 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5685</v>
+        <v>4364</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
@@ -16470,10 +16478,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>557291</v>
+        <v>557354</v>
       </c>
       <c r="R129" t="n">
-        <v>6629099</v>
+        <v>6629232</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -16521,11 +16529,6 @@
       <c r="AI129" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO129" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -16543,10 +16546,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128846508</v>
+        <v>128846350</v>
       </c>
       <c r="B130" t="n">
-        <v>92835</v>
+        <v>90921</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16554,33 +16557,25 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4364</v>
+        <v>5685</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
@@ -16589,10 +16584,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>557354</v>
+        <v>557291</v>
       </c>
       <c r="R130" t="n">
-        <v>6629232</v>
+        <v>6629099</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -16640,6 +16635,11 @@
       <c r="AI130" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>

--- a/artfynd/A 24725-2021 artfynd.xlsx
+++ b/artfynd/A 24725-2021 artfynd.xlsx
@@ -16207,7 +16207,7 @@
         <v>128846310</v>
       </c>
       <c r="B127" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>128846369</v>
       </c>
       <c r="B128" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>128846508</v>
       </c>
       <c r="B129" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>128846350</v>
       </c>
       <c r="B130" t="n">
-        <v>90921</v>
+        <v>90922</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>128846202</v>
       </c>
       <c r="B131" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>128846303</v>
       </c>
       <c r="B132" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>128846467</v>
       </c>
       <c r="B133" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>128846316</v>
       </c>
       <c r="B134" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>128846299</v>
       </c>
       <c r="B135" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>128846693</v>
       </c>
       <c r="B136" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>128846347</v>
       </c>
       <c r="B137" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>128846640</v>
       </c>
       <c r="B138" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17569,10 +17569,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128846704</v>
+        <v>128846187</v>
       </c>
       <c r="B139" t="n">
-        <v>92835</v>
+        <v>92833</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17580,26 +17580,26 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -17615,10 +17615,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>557432</v>
+        <v>557368</v>
       </c>
       <c r="R139" t="n">
-        <v>6629153</v>
+        <v>6629121</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -17665,7 +17665,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmark</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -17686,7 +17686,7 @@
         <v>128846488</v>
       </c>
       <c r="B140" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17797,10 +17797,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128846187</v>
+        <v>128846704</v>
       </c>
       <c r="B141" t="n">
-        <v>92847</v>
+        <v>92821</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17808,26 +17808,26 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -17843,10 +17843,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>557368</v>
+        <v>557432</v>
       </c>
       <c r="R141" t="n">
-        <v>6629121</v>
+        <v>6629153</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17893,7 +17893,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, hällmark</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -17914,7 +17914,7 @@
         <v>128846543</v>
       </c>
       <c r="B142" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -18025,10 +18025,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128846394</v>
+        <v>128846335</v>
       </c>
       <c r="B143" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -18071,10 +18071,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>557229</v>
+        <v>557277</v>
       </c>
       <c r="R143" t="n">
-        <v>6629256</v>
+        <v>6629049</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -18139,10 +18139,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128846335</v>
+        <v>128846394</v>
       </c>
       <c r="B144" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -18185,10 +18185,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>557277</v>
+        <v>557229</v>
       </c>
       <c r="R144" t="n">
-        <v>6629049</v>
+        <v>6629256</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -18256,7 +18256,7 @@
         <v>128846477</v>
       </c>
       <c r="B145" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 24725-2021 artfynd.xlsx
+++ b/artfynd/A 24725-2021 artfynd.xlsx
@@ -16207,7 +16207,7 @@
         <v>128846310</v>
       </c>
       <c r="B127" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>128846369</v>
       </c>
       <c r="B128" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>128846508</v>
       </c>
       <c r="B129" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>128846202</v>
       </c>
       <c r="B131" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>128846303</v>
       </c>
       <c r="B132" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16885,37 +16885,37 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128846467</v>
+        <v>128846316</v>
       </c>
       <c r="B133" t="n">
-        <v>92821</v>
+        <v>92860</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -16931,10 +16931,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>557322</v>
+        <v>557309</v>
       </c>
       <c r="R133" t="n">
-        <v>6629269</v>
+        <v>6629033</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16999,37 +16999,37 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128846316</v>
+        <v>128846467</v>
       </c>
       <c r="B134" t="n">
-        <v>92859</v>
+        <v>92822</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -17045,10 +17045,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>557309</v>
+        <v>557322</v>
       </c>
       <c r="R134" t="n">
-        <v>6629033</v>
+        <v>6629269</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -17116,7 +17116,7 @@
         <v>128846299</v>
       </c>
       <c r="B135" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>128846693</v>
       </c>
       <c r="B136" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>128846347</v>
       </c>
       <c r="B137" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17455,37 +17455,37 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128846640</v>
+        <v>128846187</v>
       </c>
       <c r="B138" t="n">
-        <v>92859</v>
+        <v>92834</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -17501,10 +17501,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>557430</v>
+        <v>557368</v>
       </c>
       <c r="R138" t="n">
-        <v>6629202</v>
+        <v>6629121</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmark</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -17569,10 +17569,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128846187</v>
+        <v>128846488</v>
       </c>
       <c r="B139" t="n">
-        <v>92833</v>
+        <v>92822</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17580,26 +17580,26 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -17615,10 +17615,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>557368</v>
+        <v>557343</v>
       </c>
       <c r="R139" t="n">
-        <v>6629121</v>
+        <v>6629242</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -17683,10 +17683,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128846488</v>
+        <v>128846704</v>
       </c>
       <c r="B140" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -17729,10 +17729,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>557343</v>
+        <v>557432</v>
       </c>
       <c r="R140" t="n">
-        <v>6629242</v>
+        <v>6629153</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -17779,7 +17779,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, hällmark</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -17797,37 +17797,37 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128846704</v>
+        <v>128846640</v>
       </c>
       <c r="B141" t="n">
-        <v>92821</v>
+        <v>92860</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -17843,10 +17843,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>557432</v>
+        <v>557430</v>
       </c>
       <c r="R141" t="n">
-        <v>6629153</v>
+        <v>6629202</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17914,7 +17914,7 @@
         <v>128846543</v>
       </c>
       <c r="B142" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -18025,37 +18025,37 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128846335</v>
+        <v>128846477</v>
       </c>
       <c r="B143" t="n">
-        <v>92821</v>
+        <v>92860</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -18071,10 +18071,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>557277</v>
+        <v>557322</v>
       </c>
       <c r="R143" t="n">
-        <v>6629049</v>
+        <v>6629269</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -18139,10 +18139,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128846394</v>
+        <v>128846335</v>
       </c>
       <c r="B144" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -18185,10 +18185,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>557229</v>
+        <v>557277</v>
       </c>
       <c r="R144" t="n">
-        <v>6629256</v>
+        <v>6629049</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -18253,37 +18253,37 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128846477</v>
+        <v>128846394</v>
       </c>
       <c r="B145" t="n">
-        <v>92859</v>
+        <v>92822</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -18299,10 +18299,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>557322</v>
+        <v>557229</v>
       </c>
       <c r="R145" t="n">
-        <v>6629269</v>
+        <v>6629256</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>

--- a/artfynd/A 24725-2021 artfynd.xlsx
+++ b/artfynd/A 24725-2021 artfynd.xlsx
@@ -16432,10 +16432,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128846508</v>
+        <v>128846350</v>
       </c>
       <c r="B129" t="n">
-        <v>92822</v>
+        <v>90922</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16443,33 +16443,25 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4364</v>
+        <v>5685</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
@@ -16478,10 +16470,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>557354</v>
+        <v>557291</v>
       </c>
       <c r="R129" t="n">
-        <v>6629232</v>
+        <v>6629099</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -16529,6 +16521,11 @@
       <c r="AI129" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -16546,10 +16543,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128846350</v>
+        <v>128846508</v>
       </c>
       <c r="B130" t="n">
-        <v>90922</v>
+        <v>92822</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16557,25 +16554,33 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5685</v>
+        <v>4364</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
@@ -16584,10 +16589,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>557291</v>
+        <v>557354</v>
       </c>
       <c r="R130" t="n">
-        <v>6629099</v>
+        <v>6629232</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -16635,11 +16640,6 @@
       <c r="AI130" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>

--- a/artfynd/A 24725-2021 artfynd.xlsx
+++ b/artfynd/A 24725-2021 artfynd.xlsx
@@ -16207,7 +16207,7 @@
         <v>128846310</v>
       </c>
       <c r="B127" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>128846369</v>
       </c>
       <c r="B128" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>128846350</v>
       </c>
       <c r="B129" t="n">
-        <v>90922</v>
+        <v>90925</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>128846508</v>
       </c>
       <c r="B130" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>128846202</v>
       </c>
       <c r="B131" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>128846303</v>
       </c>
       <c r="B132" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16885,37 +16885,37 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128846316</v>
+        <v>128846467</v>
       </c>
       <c r="B133" t="n">
-        <v>92860</v>
+        <v>92825</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -16931,10 +16931,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>557309</v>
+        <v>557322</v>
       </c>
       <c r="R133" t="n">
-        <v>6629033</v>
+        <v>6629269</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16999,37 +16999,37 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128846467</v>
+        <v>128846316</v>
       </c>
       <c r="B134" t="n">
-        <v>92822</v>
+        <v>92863</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -17045,10 +17045,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>557322</v>
+        <v>557309</v>
       </c>
       <c r="R134" t="n">
-        <v>6629269</v>
+        <v>6629033</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -17116,7 +17116,7 @@
         <v>128846299</v>
       </c>
       <c r="B135" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>128846693</v>
       </c>
       <c r="B136" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>128846347</v>
       </c>
       <c r="B137" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17455,37 +17455,37 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128846187</v>
+        <v>128846640</v>
       </c>
       <c r="B138" t="n">
-        <v>92834</v>
+        <v>92863</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -17501,10 +17501,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>557368</v>
+        <v>557430</v>
       </c>
       <c r="R138" t="n">
-        <v>6629121</v>
+        <v>6629202</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, hällmark</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -17569,10 +17569,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128846488</v>
+        <v>128846187</v>
       </c>
       <c r="B139" t="n">
-        <v>92822</v>
+        <v>92837</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17580,26 +17580,26 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -17615,10 +17615,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>557343</v>
+        <v>557368</v>
       </c>
       <c r="R139" t="n">
-        <v>6629242</v>
+        <v>6629121</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -17686,7 +17686,7 @@
         <v>128846704</v>
       </c>
       <c r="B140" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17797,37 +17797,37 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128846640</v>
+        <v>128846488</v>
       </c>
       <c r="B141" t="n">
-        <v>92860</v>
+        <v>92825</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -17843,10 +17843,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>557430</v>
+        <v>557343</v>
       </c>
       <c r="R141" t="n">
-        <v>6629202</v>
+        <v>6629242</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17893,7 +17893,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmark</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -17914,7 +17914,7 @@
         <v>128846543</v>
       </c>
       <c r="B142" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -18025,37 +18025,37 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128846477</v>
+        <v>128846394</v>
       </c>
       <c r="B143" t="n">
-        <v>92860</v>
+        <v>92825</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -18071,10 +18071,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>557322</v>
+        <v>557229</v>
       </c>
       <c r="R143" t="n">
-        <v>6629269</v>
+        <v>6629256</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -18142,7 +18142,7 @@
         <v>128846335</v>
       </c>
       <c r="B144" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18253,37 +18253,37 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128846394</v>
+        <v>128846477</v>
       </c>
       <c r="B145" t="n">
-        <v>92822</v>
+        <v>92863</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -18299,10 +18299,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>557229</v>
+        <v>557322</v>
       </c>
       <c r="R145" t="n">
-        <v>6629256</v>
+        <v>6629269</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
